--- a/artfynd/A 47297-2022 artfynd.xlsx
+++ b/artfynd/A 47297-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118467203</v>
+        <v>118467229</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565747</v>
+        <v>565695</v>
       </c>
       <c r="R2" t="n">
-        <v>7076635</v>
+        <v>7076559</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118467336</v>
+        <v>118467381</v>
       </c>
       <c r="B4" t="n">
-        <v>82263</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565631</v>
+        <v>565658</v>
       </c>
       <c r="R4" t="n">
-        <v>7076518</v>
+        <v>7076525</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118467381</v>
+        <v>118467336</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>82263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565658</v>
+        <v>565631</v>
       </c>
       <c r="R5" t="n">
-        <v>7076525</v>
+        <v>7076518</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118467229</v>
+        <v>118467203</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565695</v>
+        <v>565747</v>
       </c>
       <c r="R6" t="n">
-        <v>7076559</v>
+        <v>7076635</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118467362</v>
+        <v>118467195</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>82263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565633</v>
+        <v>565730</v>
       </c>
       <c r="R7" t="n">
-        <v>7076519</v>
+        <v>7076642</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118467195</v>
+        <v>118467362</v>
       </c>
       <c r="B8" t="n">
-        <v>82263</v>
+        <v>79565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565730</v>
+        <v>565633</v>
       </c>
       <c r="R8" t="n">
-        <v>7076642</v>
+        <v>7076519</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 47297-2022 artfynd.xlsx
+++ b/artfynd/A 47297-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118467229</v>
+        <v>118467203</v>
       </c>
       <c r="B2" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565695</v>
+        <v>565747</v>
       </c>
       <c r="R2" t="n">
-        <v>7076559</v>
+        <v>7076635</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118467466</v>
+        <v>118467195</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>82263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565827</v>
+        <v>565730</v>
       </c>
       <c r="R3" t="n">
-        <v>7076658</v>
+        <v>7076642</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -994,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118467336</v>
+        <v>118467466</v>
       </c>
       <c r="B5" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,30 +1005,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565631</v>
+        <v>565827</v>
       </c>
       <c r="R5" t="n">
-        <v>7076518</v>
+        <v>7076658</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118467203</v>
+        <v>118467362</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565747</v>
+        <v>565633</v>
       </c>
       <c r="R6" t="n">
-        <v>7076635</v>
+        <v>7076519</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118467195</v>
+        <v>118467336</v>
       </c>
       <c r="B7" t="n">
         <v>82263</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565730</v>
+        <v>565631</v>
       </c>
       <c r="R7" t="n">
-        <v>7076642</v>
+        <v>7076518</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118467362</v>
+        <v>118467229</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>90504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565633</v>
+        <v>565695</v>
       </c>
       <c r="R8" t="n">
-        <v>7076519</v>
+        <v>7076559</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 47297-2022 artfynd.xlsx
+++ b/artfynd/A 47297-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118467203</v>
+        <v>118467336</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>82270</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565747</v>
+        <v>565631</v>
       </c>
       <c r="R2" t="n">
-        <v>7076635</v>
+        <v>7076518</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118467195</v>
+        <v>118467229</v>
       </c>
       <c r="B3" t="n">
-        <v>82263</v>
+        <v>90511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565730</v>
+        <v>565695</v>
       </c>
       <c r="R3" t="n">
-        <v>7076642</v>
+        <v>7076559</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118467381</v>
+        <v>118467203</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565658</v>
+        <v>565747</v>
       </c>
       <c r="R4" t="n">
-        <v>7076525</v>
+        <v>7076635</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118467466</v>
+        <v>118467195</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>82270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,31 +1005,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565827</v>
+        <v>565730</v>
       </c>
       <c r="R5" t="n">
-        <v>7076658</v>
+        <v>7076642</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118467362</v>
+        <v>118467466</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,30 +1111,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565633</v>
+        <v>565827</v>
       </c>
       <c r="R6" t="n">
-        <v>7076519</v>
+        <v>7076658</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118467336</v>
+        <v>118467381</v>
       </c>
       <c r="B7" t="n">
-        <v>82263</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565631</v>
+        <v>565658</v>
       </c>
       <c r="R7" t="n">
-        <v>7076518</v>
+        <v>7076525</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118467229</v>
+        <v>118467362</v>
       </c>
       <c r="B8" t="n">
-        <v>90504</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565695</v>
+        <v>565633</v>
       </c>
       <c r="R8" t="n">
-        <v>7076559</v>
+        <v>7076519</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 47297-2022 artfynd.xlsx
+++ b/artfynd/A 47297-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118467336</v>
+        <v>118467203</v>
       </c>
       <c r="B2" t="n">
-        <v>82270</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565631</v>
+        <v>565747</v>
       </c>
       <c r="R2" t="n">
-        <v>7076518</v>
+        <v>7076635</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118467229</v>
+        <v>118467336</v>
       </c>
       <c r="B3" t="n">
-        <v>90511</v>
+        <v>82270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565695</v>
+        <v>565631</v>
       </c>
       <c r="R3" t="n">
-        <v>7076559</v>
+        <v>7076518</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118467203</v>
+        <v>118467466</v>
       </c>
       <c r="B4" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +899,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565747</v>
+        <v>565827</v>
       </c>
       <c r="R4" t="n">
-        <v>7076635</v>
+        <v>7076658</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118467195</v>
+        <v>118467362</v>
       </c>
       <c r="B5" t="n">
-        <v>82270</v>
+        <v>79572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565730</v>
+        <v>565633</v>
       </c>
       <c r="R5" t="n">
-        <v>7076642</v>
+        <v>7076519</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118467466</v>
+        <v>118467229</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,31 +1112,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565827</v>
+        <v>565695</v>
       </c>
       <c r="R6" t="n">
-        <v>7076658</v>
+        <v>7076559</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118467362</v>
+        <v>118467195</v>
       </c>
       <c r="B8" t="n">
-        <v>79572</v>
+        <v>82270</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565633</v>
+        <v>565730</v>
       </c>
       <c r="R8" t="n">
-        <v>7076519</v>
+        <v>7076642</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 47297-2022 artfynd.xlsx
+++ b/artfynd/A 47297-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118467229</v>
+        <v>118310623</v>
       </c>
       <c r="B2" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Snarkåsen, Ång</t>
+          <t>Skuksen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565695</v>
+        <v>565766</v>
       </c>
       <c r="R2" t="n">
-        <v>7076559</v>
+        <v>7076525</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118467195</v>
+        <v>118467229</v>
       </c>
       <c r="B3" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565730</v>
+        <v>565695</v>
       </c>
       <c r="R3" t="n">
-        <v>7076642</v>
+        <v>7076559</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,43 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118467466</v>
+        <v>118467195</v>
       </c>
       <c r="B4" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565827</v>
+        <v>565730</v>
       </c>
       <c r="R4" t="n">
-        <v>7076658</v>
+        <v>7076642</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118467381</v>
+        <v>118467336</v>
       </c>
       <c r="B5" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565658</v>
+        <v>565631</v>
       </c>
       <c r="R5" t="n">
-        <v>7076525</v>
+        <v>7076518</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118467336</v>
+        <v>118467203</v>
       </c>
       <c r="B6" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565631</v>
+        <v>565747</v>
       </c>
       <c r="R6" t="n">
-        <v>7076518</v>
+        <v>7076635</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,19 +1180,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118467203</v>
+        <v>118467381</v>
       </c>
       <c r="B7" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1249,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565747</v>
+        <v>565658</v>
       </c>
       <c r="R7" t="n">
-        <v>7076635</v>
+        <v>7076525</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,12 +1284,7 @@
         <v>118467362</v>
       </c>
       <c r="B8" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,6 +1380,108 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118467466</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Snarkåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>565827</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7076658</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47297-2022 artfynd.xlsx
+++ b/artfynd/A 47297-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118310623</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118467229</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118467195</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118467336</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118467203</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118467381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118467362</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,8 +1521,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118467466</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>